--- a/inputs/fr/LiST countries/FSM_databook.xlsx
+++ b/inputs/fr/LiST countries/FSM_databook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\fr\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{069F9B72-2837-4AD5-9464-E642E1C830FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E444940-52EE-4CF1-AF9A-FB6A11936E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Causes du décès" sheetId="3" r:id="rId3"/>
     <sheet name="Dist. de l'état nutritionnel" sheetId="4" r:id="rId4"/>
     <sheet name="Dist. l'allaitement maternel" sheetId="5" r:id="rId5"/>
-    <sheet name="Tendances temporelles" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Tendances temporelles" sheetId="6" r:id="rId6"/>
     <sheet name="Perte économique" sheetId="7" r:id="rId7"/>
     <sheet name="Paquets ANJE" sheetId="8" r:id="rId8"/>
     <sheet name="Traitement de la MAS" sheetId="9" r:id="rId9"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Données pop de l''année de ref'!$C$47</definedName>
     <definedName name="U5_mortality">'Données pop de l''année de ref'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -678,8 +678,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -692,8 +691,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -834,35 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -876,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -890,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -917,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -930,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -943,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -956,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -969,35 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1561,8 +1503,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -1732,8 +1673,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1746,8 +1686,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1760,8 +1699,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1774,8 +1712,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2138,8 +2075,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2152,7 +2088,8 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
+Insufficient published research on the intervention’s effect on the outcome.
+Thereofre, set effect of rice = effect of wheat</t>
         </r>
       </text>
     </comment>
@@ -2165,8 +2102,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2192,8 +2128,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2366,8 +2301,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2380,8 +2314,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2394,8 +2327,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2408,8 +2340,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2660,7 +2591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2669,12 +2600,37 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2688,7 +2644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2702,7 +2658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2716,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2730,7 +2686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2744,7 +2700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2758,7 +2714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2772,7 +2728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2786,7 +2742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2800,7 +2756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2814,7 +2770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2828,7 +2784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2856,7 +2812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2870,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2884,7 +2840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2911,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2924,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -2950,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -2963,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -3002,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3011,12 +2967,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3025,12 +2980,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -3039,12 +2993,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -3053,12 +3006,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3086,7 +3038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3100,7 +3052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3114,7 +3066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3142,7 +3094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3156,7 +3108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3170,7 +3122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3184,7 +3136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3198,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3212,7 +3164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3226,7 +3178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3240,7 +3192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3253,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3266,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3279,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3292,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3302,6 +3254,32 @@
           </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -4373,7 +4351,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5023,7 +5001,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5673,7 +5651,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -6941,9 +6919,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6955,9 +6932,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6969,9 +6945,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6983,9 +6958,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7118,68 +7092,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -7192,7 +7110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -7205,7 +7123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -7218,6 +7136,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
@@ -7239,9 +7209,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7253,9 +7222,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7267,9 +7235,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7281,9 +7248,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7370,7 +7336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="337">
   <si>
     <t>Field</t>
   </si>
@@ -9301,7 +9267,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="41">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9310,7 +9276,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="42">
-        <v>2030</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9328,7 +9294,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="43">
-        <v>17993008.75</v>
+        <v>18886935.875</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9360,7 +9326,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="45">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9368,7 +9334,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="45">
-        <v>0.72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9402,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="C17" s="45">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9410,7 +9376,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="45">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9418,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9427,7 +9393,7 @@
       </c>
       <c r="C20" s="46">
         <f>1-frac_rice-frac_wheat-frac_maize</f>
-        <v>0.20000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9486,7 +9452,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="45">
-        <v>0.18812535880376199</v>
+        <v>0.18812535867607999</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9494,7 +9460,7 @@
         <v>38</v>
       </c>
       <c r="C30" s="99">
-        <v>7.52921476815058E-2</v>
+        <v>7.529214782846369E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9502,7 +9468,7 @@
         <v>39</v>
       </c>
       <c r="C31" s="99">
-        <v>0.100306822402006</v>
+        <v>0.10030682254742999</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9510,7 +9476,7 @@
         <v>40</v>
       </c>
       <c r="C32" s="99">
-        <v>0.63627567111272598</v>
+        <v>0.63627567094802595</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.25">
@@ -9519,7 +9485,7 @@
       </c>
       <c r="C33" s="48">
         <f>SUM(C29:C32)</f>
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999956</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9539,7 +9505,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="43">
-        <v>27.621025084636901</v>
+        <v>26.188870000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9547,7 +9513,7 @@
         <v>45</v>
       </c>
       <c r="C38" s="43">
-        <v>36.549012265390999</v>
+        <v>34.274819999999998</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -9557,7 +9523,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="43">
-        <v>50.735712442090602</v>
+        <v>46.81147</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -9567,7 +9533,7 @@
         <v>47</v>
       </c>
       <c r="C40" s="100">
-        <v>4.01</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9583,7 +9549,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="43">
-        <v>24.614252669999999</v>
+        <v>20.564900000000002</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9600,7 +9566,7 @@
         <v>51</v>
       </c>
       <c r="C45" s="45">
-        <v>0</v>
+        <v>1.10796E-2</v>
       </c>
       <c r="D45" s="12"/>
     </row>
@@ -9609,7 +9575,7 @@
         <v>52</v>
       </c>
       <c r="C46" s="45">
-        <v>9.6231899999999995E-2</v>
+        <v>0.1180031</v>
       </c>
       <c r="D46" s="12"/>
     </row>
@@ -9618,7 +9584,7 @@
         <v>53</v>
       </c>
       <c r="C47" s="45">
-        <v>0.1543609</v>
+        <v>0.15551380000000001</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
@@ -9628,7 +9594,7 @@
         <v>54</v>
       </c>
       <c r="C48" s="46">
-        <v>0.74940719999999994</v>
+        <v>0.71540350000000008</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -9732,7 +9698,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ctgZDBIDb1i/gk5f/1TBqz2ILm9vm1EIQN8vwRJc/9x3KIJ/pmvQH/8D8vBsh2Okr/6scew2BfYTI3oZf/IvIQ==" saltValue="53nBJY1FcPjHvI4m5vwvzw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NU1pnNYjmMni2Gli4LTlnpezxTKELcJ/VLZ4bEMe0/toOCmPgyWQZLUAw8EpbyQ7F2FOKBfZQHmXKCbia3CPNg==" saltValue="e7W1qJ5UtDus5gdadgDGLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -9764,7 +9730,7 @@
       </c>
       <c r="B1" s="22" t="str">
         <f>"Couverture de l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Couverture de l'année de référence (2021)</v>
+        <v>Couverture de l'année de référence (2024)</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>166</v>
@@ -9787,7 +9753,7 @@
         <v>168</v>
       </c>
       <c r="B2" s="45">
-        <v>0.26920826853857499</v>
+        <v>0</v>
       </c>
       <c r="C2" s="98">
         <v>0.95</v>
@@ -9810,7 +9776,7 @@
         <v>169</v>
       </c>
       <c r="B3" s="45">
-        <v>0</v>
+        <v>0.36139310657109602</v>
       </c>
       <c r="C3" s="98">
         <v>0.95</v>
@@ -9862,7 +9828,7 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="56">
-        <v>2.0109515487164078</v>
+        <v>2.1334184980332371</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>201</v>
@@ -9971,7 +9937,7 @@
         <v>176</v>
       </c>
       <c r="B10" s="45">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C10" s="98">
         <v>0.95</v>
@@ -9994,7 +9960,7 @@
         <v>177</v>
       </c>
       <c r="B11" s="98">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C11" s="98">
         <v>0.95</v>
@@ -10017,7 +9983,7 @@
         <v>178</v>
       </c>
       <c r="B12" s="98">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C12" s="98">
         <v>0.95</v>
@@ -10040,7 +10006,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="98">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C13" s="98">
         <v>0.95</v>
@@ -10063,7 +10029,7 @@
         <v>180</v>
       </c>
       <c r="B14" s="45">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C14" s="98">
         <v>0.95</v>
@@ -10086,7 +10052,7 @@
         <v>181</v>
       </c>
       <c r="B15" s="98">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C15" s="98">
         <v>0.95</v>
@@ -10109,7 +10075,7 @@
         <v>182</v>
       </c>
       <c r="B16" s="45">
-        <v>0.46516892867994802</v>
+        <v>0.85</v>
       </c>
       <c r="C16" s="98">
         <v>0.95</v>
@@ -10132,7 +10098,7 @@
         <v>183</v>
       </c>
       <c r="B17" s="98">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="C17" s="98">
         <v>0.95</v>
@@ -10155,7 +10121,7 @@
         <v>157</v>
       </c>
       <c r="B18" s="98">
-        <v>0</v>
+        <v>0.215186095025478</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10178,7 +10144,7 @@
         <v>158</v>
       </c>
       <c r="B19" s="98">
-        <v>0</v>
+        <v>9.3362200000000006E-2</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10224,7 +10190,7 @@
         <v>184</v>
       </c>
       <c r="B21" s="45">
-        <v>0.3690458298</v>
+        <v>0.44068459999999998</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10270,7 +10236,7 @@
         <v>186</v>
       </c>
       <c r="B23" s="98">
-        <v>1.0999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="98">
         <v>0.95</v>
@@ -10293,7 +10259,7 @@
         <v>187</v>
       </c>
       <c r="B24" s="45">
-        <v>0.36223946720887501</v>
+        <v>0.44131542101310012</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10339,7 +10305,7 @@
         <v>189</v>
       </c>
       <c r="B26" s="45">
-        <v>0</v>
+        <v>0.1060524</v>
       </c>
       <c r="C26" s="98">
         <v>0.95</v>
@@ -10362,7 +10328,7 @@
         <v>190</v>
       </c>
       <c r="B27" s="45">
-        <v>0.27192325121491401</v>
+        <v>0</v>
       </c>
       <c r="C27" s="98">
         <v>0.95</v>
@@ -10385,7 +10351,7 @@
         <v>191</v>
       </c>
       <c r="B28" s="45">
-        <v>0.29529529999999998</v>
+        <v>0.340060866443958</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10454,7 +10420,7 @@
         <v>161</v>
       </c>
       <c r="B31" s="45">
-        <v>0.1201</v>
+        <v>0.73</v>
       </c>
       <c r="C31" s="98">
         <v>0.95</v>
@@ -10477,7 +10443,7 @@
         <v>193</v>
       </c>
       <c r="B32" s="45">
-        <v>0.56024585999999998</v>
+        <v>0</v>
       </c>
       <c r="C32" s="98">
         <v>0.95</v>
@@ -10523,7 +10489,7 @@
         <v>195</v>
       </c>
       <c r="B34" s="45">
-        <v>7.3163328954350099E-2</v>
+        <v>0.73</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10569,7 +10535,7 @@
         <v>197</v>
       </c>
       <c r="B36" s="45">
-        <v>0</v>
+        <v>0.13494429999999999</v>
       </c>
       <c r="C36" s="98">
         <v>0.95</v>
@@ -10592,7 +10558,7 @@
         <v>198</v>
       </c>
       <c r="B37" s="45">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="C37" s="98">
         <v>0.95</v>
@@ -10615,7 +10581,7 @@
         <v>199</v>
       </c>
       <c r="B38" s="45">
-        <v>0.332870572805405</v>
+        <v>0.29529529999999998</v>
       </c>
       <c r="C38" s="98">
         <v>0.95</v>
@@ -10638,7 +10604,7 @@
         <v>200</v>
       </c>
       <c r="B39" s="45">
-        <v>0.13494430539999999</v>
+        <v>0</v>
       </c>
       <c r="C39" s="98">
         <v>0.95</v>
@@ -10657,7 +10623,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="54gJsj47bR/nvKGdmhH41ZHSKyfI1dCe0LEJaeR7ujdxef83R0YsCy3F2ePjs4dBN8WDqgcSJDhVqqDOKOzV6g==" saltValue="ab19qfv8/MQuKqzlHVPt8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Pptw9ukXnNgj9gZicGnJbqyWSN292tG4xR9josYF/RRE+LZU0d4y7vJoOzuP7F91ZXDFpfjzBNeYwWqHa42r7w==" saltValue="C9JCe24K27ri4GQ77Luq0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10690,7 +10656,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>180</v>
       </c>
@@ -10699,7 +10665,7 @@
       </c>
       <c r="C2" s="47"/>
     </row>
-    <row r="3" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
         <v>181</v>
       </c>
@@ -10708,7 +10674,7 @@
       </c>
       <c r="C3" s="47"/>
     </row>
-    <row r="4" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>192</v>
       </c>
@@ -10717,7 +10683,7 @@
       </c>
       <c r="C4" s="47"/>
     </row>
-    <row r="5" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
         <v>189</v>
       </c>
@@ -10726,83 +10692,99 @@
       </c>
       <c r="C5" s="47"/>
     </row>
-    <row r="6" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C6" s="58"/>
     </row>
-    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C7" s="58"/>
     </row>
-    <row r="8" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C8" s="58"/>
     </row>
-    <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C9" s="58"/>
     </row>
-    <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
     </row>
-    <row r="11" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
     </row>
-    <row r="13" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="59"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="59"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
     </row>
-    <row r="15" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="59"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
     </row>
-    <row r="16" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="59"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
     </row>
-    <row r="17" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
     </row>
-    <row r="18" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
     </row>
-    <row r="19" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
     </row>
-    <row r="20" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KXE9lVljZfcu2fRjzC/PVS085MOMSZBr+XjRk+x1t4Rmqg3J+OCvaKxVwyOai50IpQIxrlfU3hk1OMUS7jrfiQ==" saltValue="sUv0Kh7hGJNofcmhAyLL+A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xc+vv+bD9M66gqBVQO7NFmHl12FJTwJ2CUMolu5Aj7wCURyr8QGgFeMyGKPNBH4uXkOeyBcOzzF6qI0YRw9BdA==" saltValue="BUHPoliQ+rqF8yiK3HOtaw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -10827,78 +10809,78 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
     </row>
-    <row r="11" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
     </row>
-    <row r="12" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
     </row>
-    <row r="13" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
     </row>
-    <row r="14" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
     </row>
-    <row r="15" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
     </row>
-    <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
-    <row r="17" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
     </row>
-    <row r="18" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
     </row>
-    <row r="19" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EECDeWWdhT76K5z6AyhXY2GuT4DV6RqKTOpvUJdHVFpUOhiK1wSvLmqC4I9dfIa9M2q0N7ZpO7cmhBWjR6TEmw==" saltValue="I8fBERbiVb6OjpryJYvyVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LRGFe2qkFKf4o6OTdRvnv9tsML5eVnvOjZUgTegyMcnJ9JH4MzxP7c7yYnp6URNhDsTD6N7L/H1XiQJbnxZSQA==" saltValue="ISkeLgsM9Ztl5XTf5vy5KA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -10963,23 +10945,23 @@
       </c>
       <c r="B3" s="21">
         <f>frac_mam_1month * 2.6</f>
-        <v>0.21583315780000004</v>
+        <v>0.21456214000000001</v>
       </c>
       <c r="C3" s="21">
         <f>frac_mam_1_5months * 2.6</f>
-        <v>0.21583315780000004</v>
+        <v>0.21456214000000001</v>
       </c>
       <c r="D3" s="21">
         <f>frac_mam_6_11months * 2.6</f>
-        <v>0.14125982520000002</v>
+        <v>0.13673062</v>
       </c>
       <c r="E3" s="21">
         <f>frac_mam_12_23months * 2.6</f>
-        <v>0.17237377820000002</v>
+        <v>0.16792724000000001</v>
       </c>
       <c r="F3" s="21">
         <f>frac_mam_24_59months * 2.6</f>
-        <v>0.14118899600000001</v>
+        <v>0.13748591999999998</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10988,27 +10970,27 @@
       </c>
       <c r="B4" s="21">
         <f>frac_sam_1month * 2.6</f>
-        <v>3.0770805000000002E-2</v>
+        <v>3.0589520000000002E-2</v>
       </c>
       <c r="C4" s="21">
         <f>frac_sam_1_5months * 2.6</f>
-        <v>3.0770805000000002E-2</v>
+        <v>3.0589520000000002E-2</v>
       </c>
       <c r="D4" s="21">
         <f>frac_sam_6_11months * 2.6</f>
-        <v>2.2130773340000003E-2</v>
+        <v>2.57959E-2</v>
       </c>
       <c r="E4" s="21">
         <f>frac_sam_12_23months * 2.6</f>
-        <v>3.45772648E-2</v>
+        <v>3.437018E-2</v>
       </c>
       <c r="F4" s="21">
         <f>frac_sam_24_59months * 2.6</f>
-        <v>3.1989497800000002E-2</v>
+        <v>3.1947240000000002E-2</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zb9FzLaNtc5amfG62eXEmbWRRUKo017Jq3dwR2gImWd0d5CYDBo1NLC2czYs3YPsGDPWqPuMXTfkjG98xd3BSQ==" saltValue="aYd7F56th3pVhPcHQSyMNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VM4ynNiz64YVX835KNS/+0/jOzBICi3kGekItyEgUu+DtOzKR0dabWMHouN7NL+0VQGOHM4X2njZCocpQWasjQ==" saltValue="bW5HP/Ti0ToiGYJycx0XTg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -11461,19 +11443,19 @@
       </c>
       <c r="D10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="E10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="F10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="G10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="H10" s="61">
         <v>0</v>
@@ -11807,19 +11789,19 @@
       </c>
       <c r="H18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="I18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="J18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="K18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="L18" s="61">
         <v>0</v>
@@ -12286,47 +12268,47 @@
       </c>
       <c r="E30" s="60">
         <f t="shared" ref="E30:O30" si="0">frac_maize</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12341,47 +12323,47 @@
       </c>
       <c r="E31" s="60">
         <f t="shared" ref="E31:O31" si="1">frac_rice</f>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="J31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="K31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="O31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12396,47 +12378,47 @@
       </c>
       <c r="E32" s="60">
         <f t="shared" ref="E32:O32" si="2">frac_wheat</f>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="I32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="K32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="L32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="M32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="N32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="O32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12764,7 +12746,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p9n5O9OC/g56pZZ0zXyjvvWmNOnVbpevj5q0rP+F/HqjD71CSL0vzqWpINXdfHv6Lar9/gf5Gx2sQByRUsL7zw==" saltValue="a3PnfzSvz1toKKLOwIGMpw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HujIDHKC3PZI76NDaGGjgbSSUtE7KZ9VBOvGrhzsgVspIfv7aYRm5t/NWIKfpjae00T2KgFrb3+elvPxjMv36A==" saltValue="zudyPAILImi6CqL/8dsoOg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12796,7 +12778,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ilXdzOOaTlvIGLctQjNWFyEerU0v3DP50y3OL4sPKyEneNDYF/SD0YfdewGtGpbytcUqB1worU4Ai9iYw4JbTg==" saltValue="YSxk39o8nUt7v81yPKGQtQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3bg7rTjrfVbjrc+/ibAa1KpMnZXYLtLXVBn25xLdety0/HbGUPv5m5UF+JiPiLX5EGc4sab7AfuwCipURn+VSw==" saltValue="kqadeOclypof3gDodUCwfA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12997,7 +12979,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gCHld8HkcMeVUTW6I2j8DNpqzE1klEe6CL0/KpfY/6zNcY/3zfeU0S14XGrXIxv3VTNmxRatm33/+Zw2JbPNwQ==" saltValue="l1AvZmUGOPB3OPWhxnUKiw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kg00nsPDOzAyCi8oAFiQcQvxrD1/bqgHERWdiQnKgjry3LAJM160Av2P/DvhmCVsxiOuzskT3Xta0gz8XvgXNQ==" saltValue="A/nETpOrN/E8jIXluEWuAw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14807,7 +14789,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EWGACr5v8zG+CtFbJuMnxD+FX+sausUfvq3HfxupBj3yuZHwmhvxZckB7XddwM7Di0wUiHMrC2/topswEQJFKA==" saltValue="d1TD8zxmzHHMUQRfm6+7sQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yChA5AXEwVabkSVlq7yPm2om1RgWMt2EDB3Cealv9MsEJWuqcwlBcT1hHHMXVwqaxxzkZQDYkryBWhpXo5dyCA==" saltValue="a7uj1qwl9zkWngrJKJu9Ww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14869,7 +14851,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>168</v>
       </c>
@@ -14886,7 +14868,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>169</v>
       </c>
@@ -14903,7 +14885,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>170</v>
       </c>
@@ -14920,7 +14902,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>171</v>
       </c>
@@ -14937,7 +14919,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>172</v>
       </c>
@@ -14956,7 +14938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>173</v>
       </c>
@@ -14975,7 +14957,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>174</v>
       </c>
@@ -14994,7 +14976,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>175</v>
       </c>
@@ -15013,7 +14995,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>176</v>
       </c>
@@ -15030,7 +15012,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>177</v>
       </c>
@@ -15047,7 +15029,7 @@
       <c r="J11" s="87"/>
       <c r="K11" s="87"/>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>178</v>
       </c>
@@ -15064,7 +15046,7 @@
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>179</v>
       </c>
@@ -15081,7 +15063,7 @@
       <c r="J13" s="87"/>
       <c r="K13" s="87"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>180</v>
       </c>
@@ -15100,7 +15082,7 @@
       <c r="J14" s="87"/>
       <c r="K14" s="87"/>
     </row>
-    <row r="15" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>181</v>
       </c>
@@ -15119,7 +15101,7 @@
       <c r="J15" s="87"/>
       <c r="K15" s="87"/>
     </row>
-    <row r="16" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>182</v>
       </c>
@@ -15140,7 +15122,7 @@
       <c r="J16" s="87"/>
       <c r="K16" s="87"/>
     </row>
-    <row r="17" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>183</v>
       </c>
@@ -15157,7 +15139,7 @@
       <c r="J17" s="87"/>
       <c r="K17" s="87"/>
     </row>
-    <row r="18" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>157</v>
       </c>
@@ -15176,7 +15158,7 @@
       <c r="J18" s="87"/>
       <c r="K18" s="87"/>
     </row>
-    <row r="19" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>158</v>
       </c>
@@ -15195,7 +15177,7 @@
       <c r="J19" s="87"/>
       <c r="K19" s="87"/>
     </row>
-    <row r="20" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>159</v>
       </c>
@@ -15214,7 +15196,7 @@
       <c r="J20" s="87"/>
       <c r="K20" s="87"/>
     </row>
-    <row r="21" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>184</v>
       </c>
@@ -15233,7 +15215,7 @@
       <c r="J21" s="87"/>
       <c r="K21" s="87"/>
     </row>
-    <row r="22" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>185</v>
       </c>
@@ -15570,7 +15552,7 @@
       <c r="K39" s="87"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PyE77+P+9wERvxMnMvg6wFxDm9lBP8zQtlJW4siFy8Fg5d13rXzQ0jHc3bMiC8MicTaNc4T0jOtnEFMMk9vn7w==" saltValue="kTuXRNlV3tK+aGSCzku5aw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="r8sivuIVCOxSG42xcoT91VZUvglG8h48n72pyLXIQBuImHGKhX6sFAEXOST2c8p+oi85NhW6Cii0v8YvReuheg==" saltValue="HTh8OT++EU9gu+vlDqUvQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15632,7 +15614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>109</v>
       </c>
@@ -15661,7 +15643,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -15690,7 +15672,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>97</v>
       </c>
@@ -15719,7 +15701,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>98</v>
       </c>
@@ -15748,7 +15730,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>99</v>
       </c>
@@ -15777,7 +15759,7 @@
       <c r="J6" s="87"/>
       <c r="K6" s="87"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>122</v>
       </c>
@@ -15798,7 +15780,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>123</v>
       </c>
@@ -15819,7 +15801,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>124</v>
       </c>
@@ -15840,7 +15822,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>125</v>
       </c>
@@ -15861,7 +15843,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>69</v>
       </c>
@@ -15882,7 +15864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>70</v>
       </c>
@@ -15901,7 +15883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
@@ -15920,7 +15902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>72</v>
       </c>
@@ -15940,7 +15922,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8Tt/13hMJ9GF4hIex4roEpmvIr9rPSzYSTOuDgggYBTWPo95dJoh8sxnG2cyUJW3kc7Ybi3NRZfT2gHf7D6Q5A==" saltValue="GamjjOmW9wWbKUQ/0MCyrg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CUEL+PjiakcmaqRup48aCcp6oRM2hV+zaANNbnB1SZZ3+k4q152TK8kyVg5tmjjFKtWQ2Hf7CDHaYuhSETyDgw==" saltValue="oA4WKjYKKKdim8Po5yaZFQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15991,360 +15973,398 @@
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>start_year</f>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>2584.1284000000001</v>
+        <v>2400</v>
       </c>
       <c r="C2" s="49">
-        <v>5700</v>
+        <v>7032</v>
       </c>
       <c r="D2" s="49">
-        <v>11000</v>
+        <v>10716</v>
       </c>
       <c r="E2" s="49">
-        <v>7400</v>
+        <v>7463</v>
       </c>
       <c r="F2" s="49">
-        <v>3400</v>
+        <v>4951.5</v>
       </c>
       <c r="G2" s="17">
-        <f t="shared" ref="G2:G11" si="0">C2+D2+E2+F2</f>
-        <v>27500</v>
+        <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
+        <v>30162.5</v>
       </c>
       <c r="H2" s="17">
-        <f t="shared" ref="H2:H11" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>3010.6135480171652</v>
+        <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
+        <v>2784.5364407225425</v>
       </c>
       <c r="I2" s="17">
-        <f t="shared" ref="I2:I11" si="2">G2-H2</f>
-        <v>24489.386451982835</v>
+        <f t="shared" ref="I2:I13" si="2">G2-H2</f>
+        <v>27377.963559277458</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A40" si="3">IF($A$2+ROW(A3)-2&lt;=end_year,A2+1,"")</f>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>2569.8058000000001</v>
+        <v>2415</v>
       </c>
       <c r="C3" s="50">
-        <v>5500</v>
+        <v>6952.5000000000009</v>
       </c>
       <c r="D3" s="50">
-        <v>11000</v>
+        <v>10797</v>
       </c>
       <c r="E3" s="50">
-        <v>7700</v>
+        <v>7757.5000000000009</v>
       </c>
       <c r="F3" s="50">
-        <v>3700</v>
+        <v>4968</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>27900</v>
+        <v>30475</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>2993.9271428049356</v>
+        <v>2801.9397934770582</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>24906.072857195064</v>
+        <v>27673.060206522943</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="3"/>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>2578.9279999999999</v>
+        <v>2426</v>
       </c>
       <c r="C4" s="50">
-        <v>5400</v>
+        <v>6849.5</v>
       </c>
       <c r="D4" s="50">
-        <v>10900</v>
+        <v>10881.5</v>
       </c>
       <c r="E4" s="50">
-        <v>7900</v>
+        <v>8059</v>
       </c>
       <c r="F4" s="50">
-        <v>4000</v>
+        <v>5011.5</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>28200</v>
+        <v>30801.5</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>3004.5548727999781</v>
+        <v>2814.7022521637032</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>25195.445127200022</v>
+        <v>27986.797747836295</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="3"/>
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>2587.7874000000002</v>
+        <v>2439</v>
       </c>
       <c r="C5" s="50">
-        <v>5400</v>
+        <v>6777</v>
       </c>
       <c r="D5" s="50">
-        <v>10900</v>
+        <v>10882</v>
       </c>
       <c r="E5" s="50">
-        <v>8100</v>
+        <v>8399.5</v>
       </c>
       <c r="F5" s="50">
-        <v>4400</v>
+        <v>5082.5</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>28800</v>
+        <v>31141</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>3014.8764302223199</v>
+        <v>2829.7851578842833</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>25785.123569777679</v>
+        <v>28311.214842115718</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="3"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>2596.384</v>
+        <v>2448</v>
       </c>
       <c r="C6" s="50">
-        <v>5300</v>
+        <v>6705.5000000000009</v>
       </c>
       <c r="D6" s="50">
-        <v>10700</v>
+        <v>10802.5</v>
       </c>
       <c r="E6" s="50">
-        <v>8300</v>
+        <v>8789</v>
       </c>
       <c r="F6" s="50">
-        <v>4700</v>
+        <v>5155</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>29000</v>
+        <v>31452</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>3024.8918150719601</v>
+        <v>2840.2271695369932</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>25975.108184928038</v>
+        <v>28611.772830463007</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="3"/>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>2581.2363999999998</v>
+        <v>2442</v>
       </c>
       <c r="C7" s="50">
-        <v>5200</v>
+        <v>6600</v>
       </c>
       <c r="D7" s="50">
-        <v>10600</v>
+        <v>10763.5</v>
       </c>
       <c r="E7" s="50">
-        <v>8500</v>
+        <v>9110.5</v>
       </c>
       <c r="F7" s="50">
-        <v>5000</v>
+        <v>5215.5</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>29300</v>
+        <v>31689.5</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>3007.2442516691717</v>
+        <v>2833.2658284351864</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>26292.755748330826</v>
+        <v>28856.234171564814</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="3"/>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>2565.4104000000002</v>
+        <v>2433</v>
       </c>
       <c r="C8" s="50">
-        <v>5200</v>
+        <v>6507.0000000000009</v>
       </c>
       <c r="D8" s="50">
-        <v>10500</v>
+        <v>10740.5</v>
       </c>
       <c r="E8" s="50">
-        <v>8800</v>
+        <v>9350.5</v>
       </c>
       <c r="F8" s="50">
-        <v>5400</v>
+        <v>5295.5</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>29900</v>
+        <v>31893.5</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>2988.8063249736879</v>
+        <v>2822.823816782477</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>26911.193675026312</v>
+        <v>29070.676183217522</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="3"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>2548.9059999999999</v>
+        <v>2411</v>
       </c>
       <c r="C9" s="50">
-        <v>5200</v>
+        <v>6452.5</v>
       </c>
       <c r="D9" s="50">
-        <v>10300</v>
+        <v>10717</v>
       </c>
       <c r="E9" s="50">
-        <v>9100</v>
+        <v>9508.5</v>
       </c>
       <c r="F9" s="50">
-        <v>5700</v>
+        <v>5412</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>30300</v>
+        <v>32090</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>2969.5780349855063</v>
+        <v>2797.298899409187</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>27330.421965014495</v>
+        <v>29292.701100590813</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="3"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>2531.7232000000008</v>
+        <v>2391</v>
       </c>
       <c r="C10" s="50">
-        <v>5200</v>
+        <v>6410.5000000000009</v>
       </c>
       <c r="D10" s="50">
-        <v>10200</v>
+        <v>10698</v>
       </c>
       <c r="E10" s="50">
-        <v>9300</v>
+        <v>9571</v>
       </c>
       <c r="F10" s="50">
-        <v>6000</v>
+        <v>5564.5</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>30700</v>
+        <v>32244</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>2949.5593817046297</v>
+        <v>2774.0944290698326</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>27750.440618295372</v>
+        <v>29469.905570930168</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="3"/>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>2513.8620000000001</v>
+        <v>2366</v>
       </c>
       <c r="C11" s="50">
-        <v>5200</v>
+        <v>6379.5</v>
       </c>
       <c r="D11" s="50">
-        <v>10000</v>
+        <v>10625.5</v>
       </c>
       <c r="E11" s="50">
-        <v>9400</v>
+        <v>9637.5</v>
       </c>
       <c r="F11" s="50">
-        <v>6300</v>
+        <v>5789</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>30900</v>
+        <v>32431.5</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>2928.7503651310544</v>
+        <v>2745.0888411456394</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>27971.249634868946</v>
+        <v>29686.41115885436</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+        <v>2034</v>
+      </c>
+      <c r="B12" s="49">
+        <v>2347</v>
+      </c>
+      <c r="C12" s="50">
+        <v>6359.0000000000009</v>
+      </c>
+      <c r="D12" s="50">
+        <v>10529.5</v>
+      </c>
+      <c r="E12" s="50">
+        <v>9718.5</v>
+      </c>
+      <c r="F12" s="50">
+        <v>6055</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="0"/>
+        <v>32662</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>2723.0445943232526</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="2"/>
+        <v>29938.955405676748</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+        <v>2035</v>
+      </c>
+      <c r="B13" s="49">
+        <v>2335</v>
+      </c>
+      <c r="C13" s="50">
+        <v>6352</v>
+      </c>
+      <c r="D13" s="50">
+        <v>10402.5</v>
+      </c>
+      <c r="E13" s="50">
+        <v>9800</v>
+      </c>
+      <c r="F13" s="50">
+        <v>6329</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="0"/>
+        <v>32883.5</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>2709.12191211964</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="2"/>
+        <v>30174.378087880359</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -16751,7 +16771,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rGHdsBvhGiDcUeIO9+6KDxpquB3Ti1D0O/WyutY2XPPPu1h3ZKFTKOrjw5+yIabQHYpO4zTl9qtImyi0WU/4Bw==" saltValue="dZ01Qa7B09qCJr9HHtLNqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jnNOLO3XtlV1ed1fAEHU+aXsmc4+yNv+jfSZGpwBcRz0tFU7/JK8G9bN87ITXoHMvR2SLfLQbEjTvjmvOzr97w==" saltValue="2xfjICr2DVqLAezU37fsOA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -16830,7 +16850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="104"/>
       <c r="C3" s="8" t="s">
         <v>154</v>
@@ -16852,7 +16872,7 @@
       </c>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="104"/>
       <c r="C4" s="8" t="s">
         <v>155</v>
@@ -16874,7 +16894,7 @@
       </c>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="103" t="s">
         <v>109</v>
       </c>
@@ -16882,9 +16902,7 @@
         <v>153</v>
       </c>
       <c r="D5" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -16899,15 +16917,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="104"/>
       <c r="C6" s="8" t="s">
         <v>154</v>
       </c>
       <c r="D6" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -16922,7 +16938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="104"/>
       <c r="C7" s="8" t="s">
         <v>155</v>
@@ -16943,7 +16959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="103" t="s">
         <v>96</v>
       </c>
@@ -16954,9 +16970,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>5.4438639770565089</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -16968,7 +16982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="104"/>
       <c r="C9" s="8" t="s">
         <v>154</v>
@@ -16977,9 +16991,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>5.4438639770565089</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -16991,7 +17003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="104"/>
       <c r="C10" s="8" t="s">
         <v>155</v>
@@ -17012,7 +17024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="103" t="s">
         <v>97</v>
       </c>
@@ -17035,7 +17047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="104"/>
       <c r="C12" s="8" t="s">
         <v>154</v>
@@ -17056,7 +17068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="104"/>
       <c r="C13" s="8" t="s">
         <v>155</v>
@@ -17077,7 +17089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="103" t="s">
         <v>98</v>
       </c>
@@ -17100,7 +17112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="104"/>
       <c r="C15" s="8" t="s">
         <v>154</v>
@@ -17121,7 +17133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="104"/>
       <c r="C16" s="8" t="s">
         <v>155</v>
@@ -17165,7 +17177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D18" s="86"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
@@ -17198,7 +17210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20" s="104"/>
       <c r="C20" s="8" t="s">
         <v>154</v>
@@ -17219,7 +17231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="104"/>
       <c r="C21" s="8" t="s">
         <v>155</v>
@@ -17240,7 +17252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>109</v>
       </c>
@@ -17263,7 +17275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" s="104"/>
       <c r="C23" s="8" t="s">
         <v>154</v>
@@ -17284,7 +17296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" s="104"/>
       <c r="C24" s="8" t="s">
         <v>155</v>
@@ -17305,7 +17317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>96</v>
       </c>
@@ -17328,7 +17340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" s="104"/>
       <c r="C26" s="8" t="s">
         <v>154</v>
@@ -18010,9 +18022,7 @@
         <v>153</v>
       </c>
       <c r="D58" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18037,9 +18047,7 @@
         <v>154</v>
       </c>
       <c r="D59" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18096,9 +18104,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>2.5916499681864882</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18123,9 +18129,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>2.5916499681864882</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -19355,9 +19359,7 @@
         <v>153</v>
       </c>
       <c r="D111" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="88">
         <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
@@ -19382,9 +19384,7 @@
         <v>154</v>
       </c>
       <c r="D112" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19441,9 +19441,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>93.052104168838625</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="88">
         <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
@@ -19468,9 +19466,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>93.052104168838625</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="88">
         <f t="shared" si="13"/>
@@ -20572,7 +20568,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wdg0nGmq4t9m2oRVFiz+otVTCEEemB6JAfrMvFSS4M9dOby4sKB1rJfKxoqBduwCrE7APRO/XJkOfFQ7KFnAHQ==" saltValue="Wsu6dbY7Wku0i/gRDJiFWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ht9YhF1QPjf1UsgdF2ICGngIyclSfPZt/UREiSwEDbrSVbmyoDMaq6jHLm9LF/CLtOWCC0O85/LqnJPymu8Akw==" saltValue="QwD3vLUHQIOfHUuy7J78ow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -21834,7 +21830,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gRVXl4k06/wmZAY6l7IupB2qMlJYJ6YPi9DocAMDeUmjpNp5te5QeX8XVNnHN6css5NFfEcfPAWGRR+Lk5qUgQ==" saltValue="lHw7Y0lmnf6IYuXwRuYBmw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lfB585fARpz3Tqmvk6x3zsZkP8zP24XF4LxliX0zDFkJQBHxRR0Y34ehlYzBaIJedM2fjJAqsgXpQTTBE+AyCg==" saltValue="wK+y09VzCho5xZI0CEsp0A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -29969,7 +29965,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6GFdyaUyGCRGcjgsDXYBF8OZGgUfbGMuE+RNYdSZAEmjNPZXwK3UZ4k698pQgJCiIDdHoLsAjEOjkUmBurQXDg==" saltValue="nTwGhaNa1MvANkMlxU+mOA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D7sdbwNyJVBWInXShO/VFmqQMuonAK7G/Mi2T9FlIDcof36gyno9arWksFf6BXdzhlLrzmzoJrtkeUg4PbDOAA==" saltValue="wgQL7iVpTpVb0+gpa41yuA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30078,13 +30074,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))
-/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.56198729313223428</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.54437232165648064</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30101,12 +30094,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.84108153565351818</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.83132169619856189</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="90">
         <v>1</v>
@@ -30123,12 +30114,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.84108153565351818</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.83132169619856189</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="90">
         <v>1</v>
@@ -30406,12 +30395,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.36186125043713074</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.34557014583418272</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30431,12 +30420,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.8035242307095336</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.79202817582752272</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="90">
         <f>IF(G7=1,1,G7*0.9)</f>
@@ -30456,12 +30443,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.8035242307095336</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.79202817582752272</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="90">
         <f>IF(G8=1,1,G8*0.9)</f>
@@ -30518,12 +30503,10 @@
         <v>296</v>
       </c>
       <c r="C35" s="90">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="90">
-        <f>D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="90">
         <v>1</v>
@@ -30783,12 +30766,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.89246915430525542</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.8854353687054598</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -30808,12 +30791,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.87947862134865251</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.87171724172857423</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="90">
         <f>IF(G7=1,1,G7*1.1)</f>
@@ -30833,12 +30814,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.87947862134865251</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.87171724172857423</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="90">
         <f>IF(G8=1,1,G8*1.1)</f>
@@ -30895,12 +30874,10 @@
         <v>309</v>
       </c>
       <c r="C58" s="90">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="90">
-        <f>D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="90">
         <v>1</v>
@@ -31056,7 +31033,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xSvyaTnqlPzcvd71yaXnK8FBi94Hinuw8iz0twU+RKQfukmdk2l728VWmb7bCMQcrMGtUyKJk0/odh4D3ww8YA==" saltValue="usHYCPPmDKe8KgSeBiwjDA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2PkdT9NXbikZz3YUtk3LDZ6e+L/7mKrEMXDWmTmov2tJWJkPOajKuw0pxwLr89NEBXX5gD8aXCgOi2ZGX2pQKA==" saltValue="26X01yem2BJW2BDd9sOY7w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31877,7 +31854,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="T53Us9oBmeC7tnLLAqBqLODro7uLMEu1Svhg8YlyNWO+VQ3GIVfq+6sRSpp+wEXgUFHUtV54BLUfhAOtZaPSsA==" saltValue="Phx526+xFRDD4k86eBjqBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ipgEIH2UGJJDDYBHlcaOh4av40suXw18SSaFhiocyIZm0NNSc15huLWYRwysw2OKcSBo45AT+3FbVkUQi0QJtg==" saltValue="oMBhSxUx7J2fievIq5DERQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31952,7 +31929,7 @@
         <v>171</v>
       </c>
       <c r="C3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="90">
         <v>0.53</v>
@@ -32287,16 +32264,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -32463,15 +32440,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="90">
+        <f>M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="90">
+        <f>N8</f>
         <v>0.51</v>
       </c>
       <c r="O14" s="90">
+        <f>O8</f>
         <v>0.51</v>
       </c>
     </row>
@@ -32580,59 +32561,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.72,(0.72*'Dist. de l''état nutritionnel'!E$14/(1-0.72*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.59090560190825958</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.72,(0.72*'Dist. de l''état nutritionnel'!F$14/(1-0.72*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.6477401878836162</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.72,(0.72*'Dist. de l''état nutritionnel'!G$14/(1-0.72*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.6477401878836162</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.72,(0.72*'Dist. de l''état nutritionnel'!H$14/(1-0.72*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.66062251527198679</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.72,(0.72*'Dist. de l''état nutritionnel'!I$14/(1-0.72*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.66062251527198679</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.72,(0.72*'Dist. de l''état nutritionnel'!J$14/(1-0.72*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.66062251527198679</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.72,(0.72*'Dist. de l''état nutritionnel'!K$14/(1-0.72*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.66062251527198679</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.72,(0.72*'Dist. de l''état nutritionnel'!L$14/(1-0.72*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.66355858886859564</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.72,(0.72*'Dist. de l''état nutritionnel'!M$14/(1-0.72*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.66355858886859564</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.72,(0.72*'Dist. de l''état nutritionnel'!N$14/(1-0.72*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.66355858886859564</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.72,(0.72*'Dist. de l''état nutritionnel'!O$14/(1-0.72*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.66355858886859564</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -32646,37 +32605,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <v>1</v>
+        <f t="shared" ref="E20:O20" si="0">E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -32690,59 +32660,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.8,(0.8*'Dist. de l''état nutritionnel'!E$14/(1-0.8*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.69201213298533748</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.8,(0.8*'Dist. de l''état nutritionnel'!F$14/(1-0.8*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.74095793951165911</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.8,(0.8*'Dist. de l''état nutritionnel'!G$14/(1-0.8*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.74095793951165911</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.8,(0.8*'Dist. de l''état nutritionnel'!H$14/(1-0.8*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.75173783515392267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.8,(0.8*'Dist. de l''état nutritionnel'!I$14/(1-0.8*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.75173783515392267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.8,(0.8*'Dist. de l''état nutritionnel'!J$14/(1-0.8*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.75173783515392267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.8,(0.8*'Dist. de l''état nutritionnel'!K$14/(1-0.8*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.75173783515392267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.8,(0.8*'Dist. de l''état nutritionnel'!L$14/(1-0.8*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.75417895771878085</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.8,(0.8*'Dist. de l''état nutritionnel'!M$14/(1-0.8*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.75417895771878085</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.8,(0.8*'Dist. de l''état nutritionnel'!N$14/(1-0.8*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.75417895771878085</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.8,(0.8*'Dist. de l''état nutritionnel'!O$14/(1-0.8*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.75417895771878085</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -32803,53 +32751,53 @@
         <v>171</v>
       </c>
       <c r="C26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="90">
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -32858,23 +32806,23 @@
         <v>176</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32890,19 +32838,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32911,23 +32859,23 @@
         <v>177</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32943,19 +32891,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32964,23 +32912,23 @@
         <v>178</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -32996,19 +32944,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33017,23 +32965,23 @@
         <v>179</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33049,19 +32997,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33070,39 +33018,39 @@
         <v>180</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33123,39 +33071,39 @@
         <v>181</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33176,39 +33124,39 @@
         <v>182</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33246,19 +33194,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33327,11 +33275,11 @@
         <v>189</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33344,35 +33292,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -33381,56 +33329,52 @@
         <v>190</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="90">
-        <f>M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="90">
-        <f>N32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="90">
-        <f>O32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -33438,11 +33382,11 @@
         <v>205</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33452,39 +33396,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33499,55 +33443,55 @@
         <v>173</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33556,67 +33500,45 @@
         <v>174</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.54,(0.54*'Dist. de l''état nutritionnel'!E$14/(1-0.54*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.39737645638410962</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.54,(0.54*'Dist. de l''état nutritionnel'!F$14/(1-0.54*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.45636173616923414</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.54,(0.54*'Dist. de l''état nutritionnel'!G$14/(1-0.54*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.45636173616923414</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.54,(0.54*'Dist. de l''état nutritionnel'!H$14/(1-0.54*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.4705218812587767</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.54,(0.54*'Dist. de l''état nutritionnel'!I$14/(1-0.54*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.4705218812587767</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.54,(0.54*'Dist. de l''état nutritionnel'!J$14/(1-0.54*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.4705218812587767</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.54,(0.54*'Dist. de l''état nutritionnel'!K$14/(1-0.54*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.4705218812587767</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.54,(0.54*'Dist. de l''état nutritionnel'!L$14/(1-0.54*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.47379258276327535</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.54,(0.54*'Dist. de l''état nutritionnel'!M$14/(1-0.54*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.47379258276327535</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.54,(0.54*'Dist. de l''état nutritionnel'!N$14/(1-0.54*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.47379258276327535</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.54,(0.54*'Dist. de l''état nutritionnel'!O$14/(1-0.54*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.47379258276327535</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -33624,56 +33546,56 @@
         <v>175</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33681,67 +33603,45 @@
         <v>183</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.7,(0.7*'Dist. de l''état nutritionnel'!E$14/(1-0.7*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.567227089190532</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.7,(0.7*'Dist. de l''état nutritionnel'!F$14/(1-0.7*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.62526510931915735</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.7,(0.7*'Dist. de l''état nutritionnel'!G$14/(1-0.7*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.62526510931915735</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.7,(0.7*'Dist. de l''état nutritionnel'!H$14/(1-0.7*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.63851066393541367</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.7,(0.7*'Dist. de l''état nutritionnel'!I$14/(1-0.7*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.63851066393541367</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.7,(0.7*'Dist. de l''état nutritionnel'!J$14/(1-0.7*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.63851066393541367</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.7,(0.7*'Dist. de l''état nutritionnel'!K$14/(1-0.7*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.63851066393541367</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.7,(0.7*'Dist. de l''état nutritionnel'!L$14/(1-0.7*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.6415342334807026</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.7,(0.7*'Dist. de l''état nutritionnel'!M$14/(1-0.7*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.6415342334807026</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.7,(0.7*'Dist. de l''état nutritionnel'!N$14/(1-0.7*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.6415342334807026</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.7,(0.7*'Dist. de l''état nutritionnel'!O$14/(1-0.7*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.6415342334807026</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -33802,53 +33702,53 @@
         <v>171</v>
       </c>
       <c r="C49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="90">
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -33857,23 +33757,23 @@
         <v>176</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33889,19 +33789,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33910,23 +33810,23 @@
         <v>177</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33942,19 +33842,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33963,23 +33863,23 @@
         <v>178</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -33995,19 +33895,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34016,23 +33916,23 @@
         <v>179</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -34048,19 +33948,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34069,39 +33969,39 @@
         <v>180</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34122,39 +34022,39 @@
         <v>181</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34175,52 +34075,52 @@
         <v>182</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -34246,19 +34146,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34327,11 +34227,11 @@
         <v>189</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34344,35 +34244,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34381,56 +34281,52 @@
         <v>190</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="90">
-        <f>M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="90">
-        <f>N54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="90">
-        <f>O54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34438,11 +34334,11 @@
         <v>205</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34452,39 +34348,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34499,55 +34395,55 @@
         <v>173</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -34556,67 +34452,45 @@
         <v>174</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.97,(0.97*'Dist. de l''état nutritionnel'!E$14/(1-0.97*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.94781416852962352</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.97,(0.97*'Dist. de l''état nutritionnel'!F$14/(1-0.97*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.95854300272732029</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.97,(0.97*'Dist. de l''état nutritionnel'!G$14/(1-0.97*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.95854300272732029</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.97,(0.97*'Dist. de l''état nutritionnel'!H$14/(1-0.97*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.96074788365672703</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.97,(0.97*'Dist. de l''état nutritionnel'!I$14/(1-0.97*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.96074788365672703</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.97,(0.97*'Dist. de l''état nutritionnel'!J$14/(1-0.97*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.96074788365672703</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.97,(0.97*'Dist. de l''état nutritionnel'!K$14/(1-0.97*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.96074788365672703</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.97,(0.97*'Dist. de l''état nutritionnel'!L$14/(1-0.97*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.96123980929986186</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.97,(0.97*'Dist. de l''état nutritionnel'!M$14/(1-0.97*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.96123980929986186</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.97,(0.97*'Dist. de l''état nutritionnel'!N$14/(1-0.97*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.96123980929986186</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.97,(0.97*'Dist. de l''état nutritionnel'!O$14/(1-0.97*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.96123980929986186</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -34624,56 +34498,56 @@
         <v>175</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34681,71 +34555,49 @@
         <v>183</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.92,(0.92*'Dist. de l''état nutritionnel'!E$14/(1-0.92*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.86594784878533626</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.92,(0.92*'Dist. de l''état nutritionnel'!F$14/(1-0.92*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.89158227122961131</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.92,(0.92*'Dist. de l''état nutritionnel'!G$14/(1-0.92*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.89158227122961131</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.92,(0.92*'Dist. de l''état nutritionnel'!H$14/(1-0.92*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.89696563804028639</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.92,(0.92*'Dist. de l''état nutritionnel'!I$14/(1-0.92*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.89696563804028639</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.92,(0.92*'Dist. de l''état nutritionnel'!J$14/(1-0.92*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.89696563804028639</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.92,(0.92*'Dist. de l''état nutritionnel'!K$14/(1-0.92*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.89696563804028639</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.92,(0.92*'Dist. de l''état nutritionnel'!L$14/(1-0.92*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.89817219082531452</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.92,(0.92*'Dist. de l''état nutritionnel'!M$14/(1-0.92*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.89817219082531452</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.92,(0.92*'Dist. de l''état nutritionnel'!N$14/(1-0.92*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.89817219082531452</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.92,(0.92*'Dist. de l''état nutritionnel'!O$14/(1-0.92*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.89817219082531452</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ko6Y6pHD2Gk8RdVmLN5E30GaW+xmQCPUog/k3nXGj/ysWKX3d3usr4lcY/wnDIoDlJebjmyz7kRqtYHyt/9N1w==" saltValue="E+/j6wmTzJFVAxlO3dnuJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BPVQ0rC97h4tfSi5ox6700kkJxW/6cMwqYwMpXADG2U9bhfUwW3Z+wVUEHVCpeVs3G/3PAfQA6SjFAy8SVqclg==" saltValue="JJOTEWc1a/suHEbViLgIRw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34791,7 +34643,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>161</v>
       </c>
@@ -34799,24 +34651,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.74965199256246406</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.75028153186317292</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.74937363382618449</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.749562939328692</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34830,7 +34678,7 @@
       <c r="F4" s="83"/>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>165</v>
       </c>
@@ -34838,24 +34686,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.73536216926523235</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.74131226602586131</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.73886256619599522</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.74131779020110855</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34887,7 +34731,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>161</v>
       </c>
@@ -34895,24 +34739,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.64663503384933729</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.64740178040008656</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.64629617612918244</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.64652661436258574</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34926,7 +34766,7 @@
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>165</v>
       </c>
@@ -34934,24 +34774,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.62937218488913793</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.63652745551991607</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.6335759495506228</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.63653412021811673</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34983,7 +34819,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>161</v>
       </c>
@@ -34991,24 +34827,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.86064721573245895</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.8610493750710364</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.8604693004153624</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.86059030298542916</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -35022,7 +34854,7 @@
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>165</v>
       </c>
@@ -35030,28 +34862,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.85143742375252107</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.85529126992183147</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.85370791814661429</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.85529483523571492</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ka14oQSOhY4tlWRWJqMQS6UiWn5e/Nj1v3URUr4Ul+KTLmyD5gU6f2j6JYZ4PFn5xIA8pOR7M7Ous9ZROsUNpQ==" saltValue="5CkO2+VteKQ05U7n4HWXyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KXQVihJ2zota+zjOMLhQEKr13Hb28LwwhvOciLbKEfdlUox8iJnB3hOrLBdDQI++FMaJbbWNth54AGhios5yOA==" saltValue="iEJN9S4IcLHmNkH20au1Wg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -35104,7 +34932,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>193</v>
       </c>
@@ -35130,7 +34958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>335</v>
       </c>
@@ -35150,7 +34978,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>336</v>
       </c>
@@ -35170,7 +34998,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>192</v>
       </c>
@@ -35196,7 +35024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>336</v>
       </c>
@@ -35216,7 +35044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>209</v>
       </c>
@@ -35239,7 +35067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>336</v>
       </c>
@@ -35259,7 +35087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>185</v>
       </c>
@@ -35285,7 +35113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>336</v>
       </c>
@@ -35305,7 +35133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>209</v>
       </c>
@@ -35328,7 +35156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>336</v>
       </c>
@@ -35348,7 +35176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>205</v>
       </c>
@@ -35374,7 +35202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>336</v>
       </c>
@@ -35394,7 +35222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>209</v>
       </c>
@@ -35417,7 +35245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>336</v>
       </c>
@@ -35437,7 +35265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>170</v>
       </c>
@@ -35463,7 +35291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>336</v>
       </c>
@@ -35483,7 +35311,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>209</v>
       </c>
@@ -35506,7 +35334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>336</v>
       </c>
@@ -35526,7 +35354,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>175</v>
       </c>
@@ -35552,7 +35380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>335</v>
       </c>
@@ -35572,7 +35400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>173</v>
       </c>
@@ -35598,7 +35426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>335</v>
       </c>
@@ -35618,7 +35446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>174</v>
       </c>
@@ -35644,7 +35472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>335</v>
       </c>
@@ -35664,7 +35492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>197</v>
       </c>
@@ -35690,7 +35518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>335</v>
       </c>
@@ -35710,7 +35538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>336</v>
       </c>
@@ -35730,7 +35558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>198</v>
       </c>
@@ -35756,7 +35584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>335</v>
       </c>
@@ -35776,7 +35604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>336</v>
       </c>
@@ -35796,7 +35624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>196</v>
       </c>
@@ -35822,7 +35650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>335</v>
       </c>
@@ -35842,7 +35670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C35" s="5" t="s">
         <v>336</v>
       </c>
@@ -35862,7 +35690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>195</v>
       </c>
@@ -35888,7 +35716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>335</v>
       </c>
@@ -35908,7 +35736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>336</v>
       </c>
@@ -35928,7 +35756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>194</v>
       </c>
@@ -35954,7 +35782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>335</v>
       </c>
@@ -35974,7 +35802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>336</v>
       </c>
@@ -35994,7 +35822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>200</v>
       </c>
@@ -36020,7 +35848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>335</v>
       </c>
@@ -36040,7 +35868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>336</v>
       </c>
@@ -36060,7 +35888,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>88</v>
       </c>
@@ -36083,7 +35911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>335</v>
       </c>
@@ -36103,7 +35931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C47" s="5" t="s">
         <v>336</v>
       </c>
@@ -36123,7 +35951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>191</v>
       </c>
@@ -36149,7 +35977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="5" t="s">
         <v>335</v>
       </c>
@@ -36169,7 +35997,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>199</v>
       </c>
@@ -36195,7 +36023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C51" s="5" t="s">
         <v>335</v>
       </c>
@@ -36215,7 +36043,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>184</v>
       </c>
@@ -36241,12 +36069,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C53" s="5" t="s">
         <v>335</v>
       </c>
       <c r="D53" s="90">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="90">
         <v>0</v>
@@ -36294,7 +36122,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>193</v>
       </c>
@@ -36325,7 +36153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
         <v>335</v>
       </c>
@@ -36347,7 +36175,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C59" s="5" t="s">
         <v>336</v>
       </c>
@@ -36369,7 +36197,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>192</v>
       </c>
@@ -36395,7 +36223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C61" s="5" t="s">
         <v>336</v>
       </c>
@@ -36415,7 +36243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>209</v>
       </c>
@@ -36438,7 +36266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" s="5" t="s">
         <v>336</v>
       </c>
@@ -36458,7 +36286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>185</v>
       </c>
@@ -36484,7 +36312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C65" s="5" t="s">
         <v>336</v>
       </c>
@@ -36504,7 +36332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>209</v>
       </c>
@@ -36527,7 +36355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C67" s="5" t="s">
         <v>336</v>
       </c>
@@ -36547,7 +36375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>205</v>
       </c>
@@ -36573,7 +36401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C69" s="5" t="s">
         <v>336</v>
       </c>
@@ -36596,7 +36424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>209</v>
       </c>
@@ -36624,7 +36452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C71" s="5" t="s">
         <v>336</v>
       </c>
@@ -36647,7 +36475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>170</v>
       </c>
@@ -36678,7 +36506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" s="5" t="s">
         <v>336</v>
       </c>
@@ -37502,7 +37330,7 @@
         <v>335</v>
       </c>
       <c r="D108" s="90">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="90">
         <v>0</v>
@@ -38763,7 +38591,7 @@
         <v>335</v>
       </c>
       <c r="D163" s="90">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="90">
         <v>0</v>
@@ -38779,7 +38607,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LRCWCmiIh1Ts0kex37cukq69Og0HZK7Q2vd9M3TAYfDdJmw9hWsnoVADIozdKra7h6uPXDn6oxAvmbtDtBVKcQ==" saltValue="hnqq7yl8RPfR7lsqUgPHqw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4Sm1lsbAxEA0mx7bfJr9GBxvgwgy2LO9SXzuA/7PCICO8XrIGtA42QPPCwFGcyJPhN8YHMAiS33kAwMwfB2/vg==" saltValue="qVPX0bfkdE7by20krr7+mg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -38824,7 +38652,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>169</v>
       </c>
@@ -38848,7 +38676,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
         <v>335</v>
       </c>
@@ -38866,7 +38694,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -38890,7 +38718,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
         <v>335</v>
       </c>
@@ -38908,7 +38736,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>187</v>
       </c>
@@ -38932,7 +38760,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>335</v>
       </c>
@@ -38976,7 +38804,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>169</v>
       </c>
@@ -39003,7 +38831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
         <v>335</v>
       </c>
@@ -39020,7 +38848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -39047,7 +38875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
         <v>335</v>
       </c>
@@ -39068,7 +38896,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>187</v>
       </c>
@@ -39095,7 +38923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
         <v>335</v>
       </c>
@@ -39142,7 +38970,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>169</v>
       </c>
@@ -39169,7 +38997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C21" s="8" t="s">
         <v>335</v>
       </c>
@@ -39186,7 +39014,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>188</v>
       </c>
@@ -39213,7 +39041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="8" t="s">
         <v>335</v>
       </c>
@@ -39234,7 +39062,7 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>187</v>
       </c>
@@ -39261,7 +39089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>335</v>
       </c>
@@ -39283,7 +39111,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oFn2XK79l1Pk7H4F4Hj7ZYMb1p903KW8d/KiIWcuvtdYL7g9oUe00v2yjs3vB34IvkZfh0wKWdH0Y3w11P39Og==" saltValue="VbFscMx+c90gIaFkbMJ0xA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="aQI9yKnRsexUrwfYlbwCnOj9bPsptphasbmndA68/gt3LYSWPi720b+EWdGIM8CuhjXa1zmsX7szbs852BvTWQ==" saltValue="C8HirKrj061Wd0Vnl68fpA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39305,7 +39133,7 @@
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="str">
         <f>"Pourcentage des morts de l'année de référence ("&amp;start_year&amp;") imputable à chaque cause"</f>
-        <v>Pourcentage des morts de l'année de référence (2021) imputable à chaque cause</v>
+        <v>Pourcentage des morts de l'année de référence (2024) imputable à chaque cause</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -39333,7 +39161,7 @@
         <v>78</v>
       </c>
       <c r="C3" s="55">
-        <v>7.657369944615031E-3</v>
+        <v>1.9891899999999921E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39341,7 +39169,7 @@
         <v>79</v>
       </c>
       <c r="C4" s="101">
-        <v>0.1679051777180304</v>
+        <v>7.4515400000000037E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39349,7 +39177,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="101">
-        <v>7.8118373834736701E-2</v>
+        <v>0.11823790000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39357,7 +39185,7 @@
         <v>81</v>
       </c>
       <c r="C6" s="101">
-        <v>0.29627379387842351</v>
+        <v>0.25948660000000018</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39365,7 +39193,7 @@
         <v>82</v>
       </c>
       <c r="C7" s="101">
-        <v>0.2627464776007255</v>
+        <v>0.36006529999999981</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39373,7 +39201,7 @@
         <v>83</v>
       </c>
       <c r="C8" s="101">
-        <v>1.5821735643554241E-2</v>
+        <v>4.5411999999999961E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39381,7 +39209,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="101">
-        <v>0.1059528266969353</v>
+        <v>4.8583099999999983E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39389,7 +39217,7 @@
         <v>85</v>
       </c>
       <c r="C10" s="101">
-        <v>6.552424468297928E-2</v>
+        <v>0.11467859999999989</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39398,7 +39226,7 @@
       </c>
       <c r="C11" s="48">
         <f>SUM(C3:C10)</f>
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
@@ -39438,16 +39266,16 @@
         <v>87</v>
       </c>
       <c r="C14" s="55">
-        <v>0.15015934860680141</v>
+        <v>0.19474125172663101</v>
       </c>
       <c r="D14" s="55">
-        <v>0.15015934860680141</v>
+        <v>0.19474125172663101</v>
       </c>
       <c r="E14" s="55">
-        <v>0.15015934860680141</v>
+        <v>0.19474125172663101</v>
       </c>
       <c r="F14" s="55">
-        <v>0.15015934860680141</v>
+        <v>0.19474125172663101</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39455,16 +39283,16 @@
         <v>88</v>
       </c>
       <c r="C15" s="101">
-        <v>0.26544604907649128</v>
+        <v>0.2728039497558219</v>
       </c>
       <c r="D15" s="101">
-        <v>0.26544604907649128</v>
+        <v>0.2728039497558219</v>
       </c>
       <c r="E15" s="101">
-        <v>0.26544604907649128</v>
+        <v>0.2728039497558219</v>
       </c>
       <c r="F15" s="101">
-        <v>0.26544604907649128</v>
+        <v>0.2728039497558219</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39472,16 +39300,16 @@
         <v>89</v>
       </c>
       <c r="C16" s="101">
-        <v>4.3463038117430249E-2</v>
+        <v>3.9761713379282131E-2</v>
       </c>
       <c r="D16" s="101">
-        <v>4.3463038117430249E-2</v>
+        <v>3.9761713379282131E-2</v>
       </c>
       <c r="E16" s="101">
-        <v>4.3463038117430249E-2</v>
+        <v>3.9761713379282131E-2</v>
       </c>
       <c r="F16" s="101">
-        <v>4.3463038117430249E-2</v>
+        <v>3.9761713379282131E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39489,16 +39317,16 @@
         <v>90</v>
       </c>
       <c r="C17" s="101">
-        <v>3.034588114818209E-2</v>
+        <v>8.5734847111629542E-2</v>
       </c>
       <c r="D17" s="101">
-        <v>3.034588114818209E-2</v>
+        <v>8.5734847111629542E-2</v>
       </c>
       <c r="E17" s="101">
-        <v>3.034588114818209E-2</v>
+        <v>8.5734847111629542E-2</v>
       </c>
       <c r="F17" s="101">
-        <v>3.034588114818209E-2</v>
+        <v>8.5734847111629542E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39506,16 +39334,16 @@
         <v>91</v>
       </c>
       <c r="C18" s="101">
-        <v>2.8040054880726622E-3</v>
+        <v>2.34600871035626E-2</v>
       </c>
       <c r="D18" s="101">
-        <v>2.8040054880726622E-3</v>
+        <v>2.34600871035626E-2</v>
       </c>
       <c r="E18" s="101">
-        <v>2.8040054880726622E-3</v>
+        <v>2.34600871035626E-2</v>
       </c>
       <c r="F18" s="101">
-        <v>2.8040054880726622E-3</v>
+        <v>2.34600871035626E-2</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39523,16 +39351,16 @@
         <v>92</v>
       </c>
       <c r="C19" s="101">
-        <v>3.365515816755385E-2</v>
+        <v>5.4515108223392533E-2</v>
       </c>
       <c r="D19" s="101">
-        <v>3.365515816755385E-2</v>
+        <v>5.4515108223392533E-2</v>
       </c>
       <c r="E19" s="101">
-        <v>3.365515816755385E-2</v>
+        <v>5.4515108223392533E-2</v>
       </c>
       <c r="F19" s="101">
-        <v>3.365515816755385E-2</v>
+        <v>5.4515108223392533E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39540,16 +39368,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="101">
-        <v>3.1786054073555663E-2</v>
+        <v>3.5370094976026271E-2</v>
       </c>
       <c r="D20" s="101">
-        <v>3.1786054073555663E-2</v>
+        <v>3.5370094976026271E-2</v>
       </c>
       <c r="E20" s="101">
-        <v>3.1786054073555663E-2</v>
+        <v>3.5370094976026271E-2</v>
       </c>
       <c r="F20" s="101">
-        <v>3.1786054073555663E-2</v>
+        <v>3.5370094976026271E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39557,16 +39385,16 @@
         <v>94</v>
       </c>
       <c r="C21" s="101">
-        <v>0.13649952315063441</v>
+        <v>9.0345210755778893E-2</v>
       </c>
       <c r="D21" s="101">
-        <v>0.13649952315063441</v>
+        <v>9.0345210755778893E-2</v>
       </c>
       <c r="E21" s="101">
-        <v>0.13649952315063441</v>
+        <v>9.0345210755778893E-2</v>
       </c>
       <c r="F21" s="101">
-        <v>0.13649952315063441</v>
+        <v>9.0345210755778893E-2</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39574,16 +39402,16 @@
         <v>95</v>
       </c>
       <c r="C22" s="101">
-        <v>0.30584094217127822</v>
+        <v>0.20326773696787509</v>
       </c>
       <c r="D22" s="101">
-        <v>0.30584094217127822</v>
+        <v>0.20326773696787509</v>
       </c>
       <c r="E22" s="101">
-        <v>0.30584094217127822</v>
+        <v>0.20326773696787509</v>
       </c>
       <c r="F22" s="101">
-        <v>0.30584094217127822</v>
+        <v>0.20326773696787509</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39592,19 +39420,19 @@
       </c>
       <c r="C23" s="48">
         <f>SUM(C14:C22)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="D23" s="48">
         <f>SUM(D14:D22)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="E23" s="48">
         <f>SUM(E14:E22)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="F23" s="48">
         <f>SUM(F14:F22)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -39716,7 +39544,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RTBFbRjUilXr1PhUb7SE6bQw9eQaehfWcHnJNwAtrZxg7noOnQL7dyGwGz2QdvjhRfmgcsYdf+LpzjCHiekUvw==" saltValue="eQbZbBbfN5tZXOssh3IjiA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="09D2Aashlm5dS1Vtkuvs6ixzqdo1246e+sPNPMZCIiEgJk//3Z6UPwpqJBIbII+eCbjt8H6FpSBv9GcyKHOLiA==" saltValue="wlzaEGxCeyCDCF3zJJkPhQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39738,7 +39566,7 @@
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Pourcentage de la population dans chaque catégorie pendant l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Pourcentage de la population dans chaque catégorie pendant l'année de référence (2021)</v>
+        <v>Pourcentage de la population dans chaque catégorie pendant l'année de référence (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>110</v>
@@ -39768,23 +39596,23 @@
       </c>
       <c r="C2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.47930938742751028</v>
+        <v>0.47914592269961154</v>
       </c>
       <c r="D2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.47930938742751028</v>
+        <v>0.47914592269961154</v>
       </c>
       <c r="E2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.34014292111586675</v>
+        <v>0.3522229761152027</v>
       </c>
       <c r="F2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.28965611384214496</v>
+        <v>0.29072013946907083</v>
       </c>
       <c r="G2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.20340579616572763</v>
+        <v>0.2067584686377506</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39793,23 +39621,23 @@
       </c>
       <c r="C3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE) - SUM(C4:C5), "")</f>
-        <v>0.34915466057248973</v>
+        <v>0.34921367730038844</v>
       </c>
       <c r="D3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE) - SUM(D4:D5), "")</f>
-        <v>0.34915466057248973</v>
+        <v>0.34921367730038844</v>
       </c>
       <c r="E3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.38156639788413327</v>
+        <v>0.38037002388479729</v>
       </c>
       <c r="F3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.38240453015785503</v>
+        <v>0.38246226053092913</v>
       </c>
       <c r="G3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.36427882383427235</v>
+        <v>0.3655599313622494</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39817,19 +39645,19 @@
         <v>114</v>
       </c>
       <c r="C4" s="45">
-        <v>0.13261111</v>
+        <v>0.13184029999999999</v>
       </c>
       <c r="D4" s="53">
-        <v>0.13261111</v>
+        <v>0.13184029999999999</v>
       </c>
       <c r="E4" s="53">
-        <v>0.19086748000000001</v>
+        <v>0.181427</v>
       </c>
       <c r="F4" s="53">
-        <v>0.23636545</v>
+        <v>0.2362543</v>
       </c>
       <c r="G4" s="53">
-        <v>0.28320193999999999</v>
+        <v>0.27492490000000003</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39837,19 +39665,19 @@
         <v>115</v>
       </c>
       <c r="C5" s="45">
-        <v>3.8924842000000001E-2</v>
+        <v>3.9800099999999998E-2</v>
       </c>
       <c r="D5" s="53">
-        <v>3.8924842000000001E-2</v>
+        <v>3.9800099999999998E-2</v>
       </c>
       <c r="E5" s="53">
-        <v>8.7423201000000006E-2</v>
+        <v>8.5980000000000001E-2</v>
       </c>
       <c r="F5" s="53">
-        <v>9.1573905999999997E-2</v>
+        <v>9.0563300000000013E-2</v>
       </c>
       <c r="G5" s="53">
-        <v>0.14911344000000001</v>
+        <v>0.1527567</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39877,23 +39705,23 @@
       </c>
       <c r="C8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.62228245443092634</v>
+        <v>0.62354203285300214</v>
       </c>
       <c r="D8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.62228245443092634</v>
+        <v>0.62354203285300214</v>
       </c>
       <c r="E8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.70240883725994263</v>
+        <v>0.70334224397497291</v>
       </c>
       <c r="F8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.65828626088413289</v>
+        <v>0.66275009797296724</v>
       </c>
       <c r="G8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.6920067782465521</v>
+        <v>0.69595062527720364</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39902,23 +39730,23 @@
       </c>
       <c r="C9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE) - SUM(C10:C11), "")</f>
-        <v>0.28286986756907367</v>
+        <v>0.28216886714699779</v>
       </c>
       <c r="D9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE) - SUM(D10:D11), "")</f>
-        <v>0.28286986756907367</v>
+        <v>0.28216886714699779</v>
       </c>
       <c r="E9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE) - SUM(E10:E11), "")</f>
-        <v>0.23474862484005732</v>
+        <v>0.23414755602502707</v>
       </c>
       <c r="F9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE) - SUM(F10:F11), "")</f>
-        <v>0.2621171841158671</v>
+        <v>0.25944320202703269</v>
       </c>
       <c r="G9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE) - SUM(G10:G11), "")</f>
-        <v>0.2413861087534479</v>
+        <v>0.23888277472279631</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39926,19 +39754,19 @@
         <v>119</v>
       </c>
       <c r="C10" s="45">
-        <v>8.3012753000000009E-2</v>
+        <v>8.2523899999999997E-2</v>
       </c>
       <c r="D10" s="53">
-        <v>8.3012753000000009E-2</v>
+        <v>8.2523899999999997E-2</v>
       </c>
       <c r="E10" s="53">
-        <v>5.4330702000000002E-2</v>
+        <v>5.2588700000000002E-2</v>
       </c>
       <c r="F10" s="53">
-        <v>6.6297607000000008E-2</v>
+        <v>6.4587400000000003E-2</v>
       </c>
       <c r="G10" s="53">
-        <v>5.4303459999999998E-2</v>
+        <v>5.2879199999999987E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39946,19 +39774,19 @@
         <v>120</v>
       </c>
       <c r="C11" s="45">
-        <v>1.1834925E-2</v>
+        <v>1.17652E-2</v>
       </c>
       <c r="D11" s="53">
-        <v>1.1834925E-2</v>
+        <v>1.17652E-2</v>
       </c>
       <c r="E11" s="53">
-        <v>8.5118359000000005E-3</v>
+        <v>9.9214999999999998E-3</v>
       </c>
       <c r="F11" s="53">
-        <v>1.3298948E-2</v>
+        <v>1.32193E-2</v>
       </c>
       <c r="G11" s="53">
-        <v>1.2303652999999999E-2</v>
+        <v>1.22874E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -40135,7 +39963,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LyafJAUucyPOobej2qWvKEypgI9tydv1Ehn0ipZNGSQNJedS5PXfxv1Bj91uwGomg6HBrHitZhmhmrQfuttFiQ==" saltValue="w4S2quuO2IKAPfVCKcDVbg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4hGb0C/0KMz9g4u52TRRpW81u3clyM0J6wZW/13Sb/l3wNsxKebJbiuar9M49dIgnrlqVcl6hSNHSykrhaiVFA==" saltValue="nmnip6Idei2xv2olOoP7xg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40157,7 +39985,7 @@
     <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Pourcentage des enfants dans chaque catégorie pendant l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Pourcentage des enfants dans chaque catégorie pendant l'année de référence (2021)</v>
+        <v>Pourcentage des enfants dans chaque catégorie pendant l'année de référence (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>110</v>
@@ -40186,64 +40014,78 @@
         <v>129</v>
       </c>
       <c r="C2" s="45">
-        <v>0.73135047909999995</v>
+        <v>0.73135050000000001</v>
       </c>
       <c r="D2" s="53">
-        <v>0.56024585999999998</v>
-      </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+        <v>0.56024590000000007</v>
+      </c>
+      <c r="E2" s="53">
+        <v>0</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C3" s="53">
-        <v>0.10681968</v>
+        <v>0.1068197</v>
       </c>
       <c r="D3" s="53">
-        <v>0.15972823</v>
-      </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
+        <v>0.15972819999999999</v>
+      </c>
+      <c r="E3" s="53">
+        <v>0</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0</v>
+      </c>
+      <c r="G3" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="53">
-        <v>8.5384884000000008E-2</v>
+        <v>8.53849E-2</v>
       </c>
       <c r="D4" s="53">
-        <v>0.22809884999999999</v>
+        <v>0.22809889999999999</v>
       </c>
       <c r="E4" s="53">
-        <v>0.94018203020095792</v>
+        <v>0.93737269999999995</v>
       </c>
       <c r="F4" s="53">
-        <v>0.84757745265960693</v>
-      </c>
-      <c r="G4" s="53"/>
+        <v>0.81075520000000001</v>
+      </c>
+      <c r="G4" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C5" s="52">
-        <v>7.6444969180000003E-2</v>
+        <v>7.6444999999999999E-2</v>
       </c>
       <c r="D5" s="52">
-        <v>5.1927031999999998E-2</v>
+        <v>5.1927000000000001E-2</v>
       </c>
       <c r="E5" s="52">
         <f>1-SUM(E2:E4)</f>
-        <v>5.9817969799042081E-2</v>
+        <v>6.2627300000000052E-2</v>
       </c>
       <c r="F5" s="52">
         <f>1-SUM(F2:F4)</f>
-        <v>0.15242254734039307</v>
+        <v>0.18924479999999999</v>
       </c>
       <c r="G5" s="52">
         <f>1-SUM(G2:G4)</f>
@@ -40251,7 +40093,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/YDdLetguEKgL/NZvuGtr4vzoxUA8b55y93fRTOGaGMDVmbGmdUV+VlTAt4Y47MrKFv+ZK2VA+HKJbZCHC+dTA==" saltValue="Z4R3xxj+Yl6AiNDOC8JMZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="V/RpjNqa7yCUglNEj3aYShKnIlcgJikXG7GhqNSZAbCKa2agVYAC5vKdnYTPRX4NYJDtL5GL4zyg+K4NElTB1w==" saltValue="Nd2uyvEJMEVWyNB6Jea/GQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40304,7 +40146,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>134</v>
       </c>
@@ -40321,10 +40163,10 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -40341,10 +40183,10 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -40361,7 +40203,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>100</v>
       </c>
@@ -40375,7 +40217,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>137</v>
       </c>
@@ -40389,7 +40231,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -40406,7 +40248,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>140</v>
       </c>
@@ -40420,7 +40262,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>43</v>
       </c>
@@ -40437,7 +40279,7 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>142</v>
       </c>
@@ -40452,7 +40294,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bww6d4A7PVDBx0soimZUqnX7ejDuyfZ5rlcM0PeCO7mTYcUVPrCJGmIXnlyrAFtzdOtSgpEJfQsIfmXR/ZFFwQ==" saltValue="wPsRiKCbNwbBaAe0SMzzfA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2rf7oNbOpKraPUzmEk9+zUowN5yEgv8os+oSA2nKwGQw+xp9p+mzWGgmtyIWXYZBXSB2i5JplcPG2yjX5VsRvg==" saltValue="7wlgxs511oeLqP0U9p44Ag==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -40478,7 +40320,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>145</v>
       </c>
@@ -40486,7 +40328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>150</v>
       </c>
@@ -40494,7 +40336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>146</v>
       </c>
@@ -40502,7 +40344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>147</v>
       </c>
@@ -40510,7 +40352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>148</v>
       </c>
@@ -40518,7 +40360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>149</v>
       </c>
@@ -40527,7 +40369,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fG7MxnIkuOrfI9OLW8uBnYqhpAoW/8Pgj+sWRcMMTty3b06enBYHRadeVvJeFNSpIWsP7kbePc2NQLaq0sOibQ==" saltValue="tKtA7lFLc+2vo9/eoPBPEA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uT2eu4FnnX4UM0AdKemc2UlSjPX/S3BXjNQWQBaWJj+lRZk944lbOHug3i+rQl6FLp4gW3uGFv8Fvhwyulm4mg==" saltValue="BuxSTNpzqpeXyvsxfWyHWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40579,7 +40421,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>109</v>
       </c>
@@ -40592,7 +40434,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>96</v>
       </c>
@@ -40605,29 +40447,33 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E5" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>98</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E6" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
         <v>156</v>
       </c>
@@ -40649,7 +40495,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>109</v>
       </c>
@@ -40660,7 +40506,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>96</v>
       </c>
@@ -40671,7 +40517,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="32" t="s">
         <v>97</v>
       </c>
@@ -40684,7 +40530,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="32" t="s">
         <v>98</v>
       </c>
@@ -40697,7 +40543,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
         <v>156</v>
       </c>
@@ -40721,7 +40567,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
         <v>109</v>
       </c>
@@ -40734,7 +40580,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>96</v>
       </c>
@@ -40747,7 +40593,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
         <v>97</v>
       </c>
@@ -40760,7 +40606,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="32" t="s">
         <v>98</v>
       </c>
@@ -40773,7 +40619,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
         <v>156</v>
       </c>
@@ -40782,7 +40628,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FdvZm+FajThm1h1t3d5uXrw55OqRI/6+/2ZuQlioL//Xn8qE0nUkt1gyL1MW2hr0RU6xuRA4g2MHpIK3BLljsw==" saltValue="mX5c4lPG1o41n0kt8jqzmQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B+alaqZM6Et95KLhuWOZ8FeXDzirkbzFhVtprAoE7TDMDCeVmaDl4fuplw1Ig3z1EVQYKHqOovlW3Tp8zlqrew==" saltValue="i0i4oujAZyk7B2lLTpl4Pw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -40841,7 +40687,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZCn8Z1NuffA5wDbWZrFu7r+5LyLs02n38kq4BiXK6/GdOQ3Yz+D5J+r5dLI+SYZQUjg6MQSe22I3t28HJqc/2g==" saltValue="Zs/kioTRfMH4lVtePjkiuA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dnvLXe6DzUErvU2glkxKFT4kAFjc46j21dC6ihRiHDysSeaRVMXQ1I94VB/W+gJaQHzO67foBpCnQGqc9i6xYg==" saltValue="bVn5nBhrGJufdnW4nhYNNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>